--- a/outputs/tables/FINAL_results_main_all.xlsx
+++ b/outputs/tables/FINAL_results_main_all.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_n363" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_n381" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -508,7 +508,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AIP Low/High = 191/172; DISC No/With = 161/202; below the N_main=400 target -&gt; interim / exploratory</t>
+          <t>AIP Low/High = 202/179; DISC No/With = 169/212; below the N_main=400 target -&gt; interim / exploratory</t>
         </is>
       </c>
     </row>
@@ -525,11 +525,11 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>mean 4.85, SD 1.38</t>
+          <t>mean 4.82, SD 1.39</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>alpha 0.910, rhoA 0.911, CR 0.933, AVE 0.736; min 1.00 max 7.00; skew -1.11</t>
+          <t>alpha 0.913, rhoA 0.914, CR 0.935, AVE 0.742; min 1.00 max 7.00; skew -1.08</t>
         </is>
       </c>
     </row>
@@ -560,11 +560,11 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mean 5.27, SD 1.21</t>
+          <t>mean 5.24, SD 1.25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>alpha 0.907, rhoA 0.909, CR 0.935, AVE 0.783; min 1.00 max 7.00; skew -1.23</t>
+          <t>alpha 0.915, rhoA 0.916, CR 0.940, AVE 0.797; min 1.00 max 7.00; skew -1.28</t>
         </is>
       </c>
     </row>
@@ -595,11 +595,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mean 3.32, SD 1.28</t>
+          <t>mean 3.34, SD 1.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>alpha 0.904, rhoA 0.904, CR 0.929, AVE 0.723; min 1.00 max 6.80; skew 0.25</t>
+          <t>alpha 0.907, rhoA 0.908, CR 0.931, AVE 0.730; min 1.00 max 7.00; skew 0.26</t>
         </is>
       </c>
     </row>
@@ -630,11 +630,11 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mean 4.71, SD 1.09</t>
+          <t>mean 4.70, SD 1.11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>alpha 0.911, rhoA 0.923, CR 0.931, AVE 0.692; min 1.17 max 7.00; skew -0.52</t>
+          <t>alpha 0.915, rhoA 0.926, CR 0.933, AVE 0.701; min 1.00 max 7.00; skew -0.57</t>
         </is>
       </c>
     </row>
@@ -665,11 +665,11 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>mean 5.05, SD 0.93</t>
+          <t>mean 5.06, SD 0.93</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>alpha 0.864, rhoA 0.869, CR 0.898, AVE 0.595; min 2.33 max 7.00; skew -0.39</t>
+          <t>alpha 0.865, rhoA 0.870, CR 0.898, AVE 0.596; min 2.33 max 7.00; skew -0.39</t>
         </is>
       </c>
     </row>
@@ -700,11 +700,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>mean 5.19, SD 0.92</t>
+          <t>mean 5.18, SD 0.93</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>alpha 0.867, rhoA 0.873, CR 0.909, AVE 0.714; min 2.00 max 7.00; skew -0.55</t>
+          <t>alpha 0.866, rhoA 0.872, CR 0.909, AVE 0.714; min 2.00 max 7.00; skew -0.55</t>
         </is>
       </c>
     </row>
@@ -735,11 +735,11 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>mean 5.88, SD 1.12</t>
+          <t>mean 5.87, SD 1.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>alpha 0.871, rhoA 0.910, CR 0.909, AVE 0.715; min 1.00 max 7.00; skew -1.87</t>
+          <t>alpha 0.871, rhoA 0.908, CR 0.909, AVE 0.715; min 1.00 max 7.00; skew -1.82</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -801,11 +801,11 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>47.4% High AIP</t>
+          <t>47.0% High AIP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -832,11 +832,11 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>max 0.812 (AIP-REL 0.812)</t>
+          <t>max 0.822 (AIP-REL 0.822)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -863,11 +863,11 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>max inner VIF 1.16; max outer VIF 3.26</t>
+          <t>max inner VIF 1.17; max outer VIF 3.44</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>beta=0.740</t>
+          <t>beta=0.753</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>t=22.33</t>
+          <t>t=24.50</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[0.670, 0.800]</t>
+          <t>[0.689, 0.809]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>f2=1.209</t>
+          <t>f2=1.307</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1164,26 +1164,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>beta=0.038</t>
+          <t>beta=0.023</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>t=0.60</t>
+          <t>t=0.37</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[-0.088, 0.162]</t>
+          <t>[-0.102, 0.143]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1215,31 +1215,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>beta=0.220</t>
+          <t>beta=0.211</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>t=2.96</t>
+          <t>t=2.94</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[0.077, 0.371]</t>
+          <t>[0.073, 0.352]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>f2=0.054</t>
+          <t>f2=0.051</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1266,36 +1266,36 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>beta=0.136</t>
+          <t>beta=0.086</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>t=1.94</t>
+          <t>t=1.24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[0.001, 0.273]</t>
+          <t>[-0.047, 0.221]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>f2=0.021</t>
+          <t>f2=0.008</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Supported</t>
+          <t>Not supported</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>beta=-0.226</t>
+          <t>beta=-0.254</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>t=-3.41</t>
+          <t>t=-3.87</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[-0.358, -0.098]</t>
+          <t>[-0.382, -0.125]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>f2=0.061</t>
+          <t>f2=0.078</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1368,31 +1368,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>beta=-0.051</t>
+          <t>beta=-0.048</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>t=-0.86</t>
+          <t>t=-0.81</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[-0.168, 0.064]</t>
+          <t>[-0.162, 0.068]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>f2=0.003</t>
+          <t>f2=0.002</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1419,31 +1419,31 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>beta=-0.115</t>
+          <t>beta=-0.147</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>t=-2.53</t>
+          <t>t=-3.21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[-0.205, -0.029]</t>
+          <t>[-0.240, -0.059]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>f2=0.021</t>
+          <t>f2=0.035</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>beta=0.348</t>
+          <t>beta=0.361</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>t=4.95</t>
+          <t>t=5.28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[0.209, 0.487]</t>
+          <t>[0.228, 0.495]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>f2=0.128</t>
+          <t>f2=0.135</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>beta=0.600</t>
+          <t>beta=0.582</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>t=12.81</t>
+          <t>t=12.28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[0.505, 0.689]</t>
+          <t>[0.488, 0.672]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>f2=0.580</t>
+          <t>f2=0.539</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1568,31 +1568,31 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>beta=-0.031</t>
+          <t>beta=-0.043</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>t=-0.58</t>
+          <t>t=-0.82</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[-0.135, 0.074]</t>
+          <t>[-0.145, 0.063]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>0.421</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>f2=0.001</t>
+          <t>f2=0.002</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1611,26 +1611,26 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>beta=0.083</t>
+          <t>beta=0.084</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>t=1.68</t>
+          <t>t=1.72</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[-0.014, 0.180]</t>
+          <t>[-0.011, 0.179]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.085</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1654,26 +1654,26 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>beta=0.116</t>
+          <t>beta=0.105</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>t=2.05</t>
+          <t>t=1.99</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[0.012, 0.230]</t>
+          <t>[0.007, 0.215]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.035</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1701,31 +1701,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>beta=-0.088</t>
+          <t>beta=-0.110</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>t=-1.27</t>
+          <t>t=-1.69</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[-0.224, 0.045]</t>
+          <t>[-0.235, 0.020]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>f2=0.010</t>
+          <t>f2=0.015</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1752,31 +1752,31 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>beta=-0.048</t>
+          <t>beta=0.004</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>t=-0.71</t>
+          <t>t=0.06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[-0.184, 0.080]</t>
+          <t>[-0.130, 0.132]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>0.998</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>f2=0.003</t>
+          <t>f2=0.000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1799,33 +1799,33 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>0.076</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[0.024, 0.145]</t>
+          <t>[0.024, 0.142]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Complementary (partial)</t>
+          <t>Indirect-only mediation (full)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>direct beta 0.136 (p=0.048)</t>
+          <t>direct beta 0.086 (p=0.218)</t>
         </is>
       </c>
     </row>
@@ -1842,17 +1842,17 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-0.079</t>
+          <t>-0.092</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[-0.138, -0.031]</t>
+          <t>[-0.155, -0.039]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>direct beta -0.051 (p=0.388)</t>
+          <t>direct beta -0.048 (p=0.415)</t>
         </is>
       </c>
     </row>
@@ -1885,22 +1885,22 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[0.000, 0.167]</t>
+          <t>[-0.027, 0.132]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1928,22 +1928,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[-0.099, 0.040]</t>
+          <t>[-0.093, 0.041]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>direct beta -0.115 (p=0.009)</t>
+          <t>direct beta -0.147 (p=0.001)</t>
         </is>
       </c>
     </row>
@@ -1971,22 +1971,22 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[0.014, 0.090]</t>
+          <t>[0.013, 0.087]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -2014,17 +2014,17 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-0.047</t>
+          <t>-0.053</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[-0.087, -0.018]</t>
+          <t>[-0.095, -0.022]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>direct beta -0.115 (p=0.009)</t>
+          <t>direct beta -0.147 (p=0.001)</t>
         </is>
       </c>
     </row>
@@ -2061,37 +2061,37 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>b=-0.075</t>
+          <t>b=-0.092</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[-0.193, 0.013] BCa</t>
+          <t>[-0.207, -0.005] BCa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>boot 0.112 (no Holm adjustment, A-22)</t>
+          <t>boot 0.047 (no Holm adjustment, A-22)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>f2=0.0123</t>
+          <t>f2=0.0179</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>CI includes 0 -&gt; not supported</t>
+          <t>CI excludes 0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>classical p=0.037; HC3 p=0.154; R2=0.153</t>
+          <t>classical p=0.010; HC3 p=0.077; R2=0.165</t>
         </is>
       </c>
     </row>
@@ -2108,22 +2108,22 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>slope=-0.104</t>
+          <t>slope=-0.110</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[-0.242, 0.084] BCa</t>
+          <t>[-0.251, 0.065] BCa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>boot 0.218</t>
+          <t>boot 0.180</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2147,22 +2147,22 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>slope=-0.188</t>
+          <t>slope=-0.213</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[-0.297, -0.074] BCa</t>
+          <t>[-0.322, -0.097] BCa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>boot 0.001</t>
+          <t>boot 0.000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2186,22 +2186,22 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>slope=-0.273</t>
+          <t>slope=-0.315</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[-0.426, -0.100] BCa</t>
+          <t>[-0.472, -0.158] BCa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>boot 0.001</t>
+          <t>boot 0.000</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2229,37 +2229,37 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>b=-0.051</t>
+          <t>b=-0.072</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[-0.102, 0.001] BCa</t>
+          <t>[-0.126, -0.018] BCa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>boot 0.050 (no Holm adjustment, A-22)</t>
+          <t>boot 0.018 (no Holm adjustment, A-22)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>f2=0.0071</t>
+          <t>f2=0.0120</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>CI includes 0 -&gt; not supported</t>
+          <t>CI excludes 0</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>classical p=0.129; HC3 p=0.037; R2=0.285</t>
+          <t>classical p=0.044; HC3 p=0.004; R2=0.278</t>
         </is>
       </c>
     </row>
@@ -2276,22 +2276,22 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>slope=-0.129</t>
+          <t>slope=-0.119</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[-0.224, -0.040] BCa</t>
+          <t>[-0.209, -0.030] BCa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>boot 0.008</t>
+          <t>boot 0.012</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>slope=-0.186</t>
+          <t>slope=-0.200</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[-0.263, -0.112] BCa</t>
+          <t>[-0.279, -0.127] BCa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>slope=-0.244</t>
+          <t>slope=-0.280</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[-0.345, -0.146] BCa</t>
+          <t>[-0.389, -0.183] BCa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2397,27 +2397,27 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>b=-0.093</t>
+          <t>b=-0.002</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[-0.318, 0.138] BCa</t>
+          <t>[-0.233, 0.230] BCa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>boot 0.415 (no Holm adjustment, A-22)</t>
+          <t>boot 0.978 (no Holm adjustment, A-22)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>f2=0.0033</t>
+          <t>f2=0.0000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>classical p=0.279; HC3 p=0.440; R2=0.146</t>
+          <t>classical p=0.978; HC3 p=0.984; R2=0.150</t>
         </is>
       </c>
     </row>
@@ -2444,22 +2444,22 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>slope=-0.139</t>
+          <t>slope=-0.218</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[-0.334, 0.038] BCa</t>
+          <t>[-0.407, -0.033] BCa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>boot 0.137</t>
+          <t>boot 0.024</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2483,22 +2483,22 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>slope=-0.232</t>
+          <t>slope=-0.220</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[-0.369, -0.085] BCa</t>
+          <t>[-0.355, -0.078] BCa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>boot 0.001</t>
+          <t>boot 0.002</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2526,27 +2526,27 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>b=-0.069</t>
+          <t>b=-0.038</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[-0.219, 0.088] BCa</t>
+          <t>[-0.182, 0.111] BCa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>boot 0.394 (no Holm adjustment, A-22)</t>
+          <t>boot 0.612 (no Holm adjustment, A-22)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>f2=0.0025</t>
+          <t>f2=0.0008</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>classical p=0.367; HC3 p=0.383; R2=0.279</t>
+          <t>classical p=0.607; HC3 p=0.616; R2=0.275</t>
         </is>
       </c>
     </row>
@@ -2573,22 +2573,22 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>slope=-0.157</t>
+          <t>slope=-0.169</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[-0.281, -0.035] BCa</t>
+          <t>[-0.286, -0.049] BCa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>boot 0.011</t>
+          <t>boot 0.004</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2612,17 +2612,17 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>slope=-0.226</t>
+          <t>slope=-0.207</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[-0.316, -0.130] BCa</t>
+          <t>[-0.298, -0.119] BCa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">

--- a/outputs/tables/FINAL_results_main_all.xlsx
+++ b/outputs/tables/FINAL_results_main_all.xlsx
@@ -1692,14 +1692,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H7a INT x PDPL -&gt; TRU (beta_M1)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>- (dampening, A-22)</t>
-        </is>
-      </c>
+          <t>spec INT*PDPL-&gt;TRU (H7a tested via OLS Hayes PROCESS Model 1, Section G, not here)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
         <v>381</v>
       </c>
@@ -1728,11 +1724,7 @@
           <t>f2=0.015</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Not supported</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1743,14 +1735,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H7b INT x DISC -&gt; TRU (beta_M2)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>- (dampening, A-23)</t>
-        </is>
-      </c>
+          <t>spec INT*DISC-&gt;TRU (H7b tested via OLS Hayes PROCESS Model 1, Section G, not here)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
         <v>381</v>
       </c>
@@ -1779,11 +1767,7 @@
           <t>f2=0.000</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Not supported</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2047,7 +2031,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2057,7 +2041,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dampening, beta_M &lt; 0 (A-22/A-23)</t>
+          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2076,7 +2060,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>boot 0.047 (no Holm adjustment, A-22)</t>
+          <t>boot 0.047 (no Holm adjustment)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2098,7 +2082,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2137,7 +2121,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2176,7 +2160,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2215,7 +2199,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2225,7 +2209,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dampening, beta_M &lt; 0 (A-22/A-23)</t>
+          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2244,7 +2228,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>boot 0.018 (no Holm adjustment, A-22)</t>
+          <t>boot 0.018 (no Holm adjustment)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2266,7 +2250,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2305,7 +2289,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2344,7 +2328,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2383,7 +2367,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2393,7 +2377,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dampening, beta_M &lt; 0 (A-22/A-23)</t>
+          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2412,7 +2396,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>boot 0.978 (no Holm adjustment, A-22)</t>
+          <t>boot 0.978 (no Holm adjustment)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2434,7 +2418,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2473,7 +2457,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2512,7 +2496,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2522,7 +2506,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dampening, beta_M &lt; 0 (A-22/A-23)</t>
+          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2541,7 +2525,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>boot 0.612 (no Holm adjustment, A-22)</t>
+          <t>boot 0.612 (no Holm adjustment)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2563,7 +2547,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2602,7 +2586,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>G. OLS model of record (TF v2.13 A-22/A-23; INTERIM, Hayes PROCESS Model 1, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">

--- a/outputs/tables/FINAL_results_main_all.xlsx
+++ b/outputs/tables/FINAL_results_main_all.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_n381" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="main_n404" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -508,7 +508,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AIP Low/High = 202/179; DISC No/With = 169/212; below the N_main=400 target -&gt; interim / exploratory</t>
+          <t>AIP Low/High = 209/195; DISC No/With = 177/227; below the N_main=400 target -&gt; interim / exploratory</t>
         </is>
       </c>
     </row>
@@ -525,11 +525,11 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>mean 4.82, SD 1.39</t>
+          <t>mean 4.83, SD 1.37</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>alpha 0.913, rhoA 0.914, CR 0.935, AVE 0.742; min 1.00 max 7.00; skew -1.08</t>
+          <t>alpha 0.913, rhoA 0.914, CR 0.935, AVE 0.742; min 1.00 max 7.00; skew -1.12</t>
         </is>
       </c>
     </row>
@@ -560,11 +560,11 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>mean 5.24, SD 1.25</t>
+          <t>mean 5.25, SD 1.24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>alpha 0.915, rhoA 0.916, CR 0.940, AVE 0.797; min 1.00 max 7.00; skew -1.28</t>
+          <t>alpha 0.915, rhoA 0.916, CR 0.940, AVE 0.797; min 1.00 max 7.00; skew -1.31</t>
         </is>
       </c>
     </row>
@@ -595,11 +595,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>mean 3.34, SD 1.29</t>
+          <t>mean 3.37, SD 1.30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -630,11 +630,11 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>mean 4.70, SD 1.11</t>
+          <t>mean 4.68, SD 1.10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>alpha 0.915, rhoA 0.926, CR 0.933, AVE 0.701; min 1.00 max 7.00; skew -0.57</t>
+          <t>alpha 0.915, rhoA 0.926, CR 0.933, AVE 0.701; min 1.00 max 7.00; skew -0.54</t>
         </is>
       </c>
     </row>
@@ -665,11 +665,11 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>mean 5.06, SD 0.93</t>
+          <t>mean 5.06, SD 0.92</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>alpha 0.865, rhoA 0.870, CR 0.898, AVE 0.596; min 2.33 max 7.00; skew -0.39</t>
+          <t>alpha 0.865, rhoA 0.870, CR 0.898, AVE 0.596; min 2.33 max 7.00; skew -0.38</t>
         </is>
       </c>
     </row>
@@ -700,11 +700,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>mean 5.18, SD 0.93</t>
+          <t>mean 5.17, SD 0.93</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>alpha 0.866, rhoA 0.872, CR 0.909, AVE 0.714; min 2.00 max 7.00; skew -0.55</t>
+          <t>alpha 0.866, rhoA 0.872, CR 0.909, AVE 0.714; min 2.00 max 7.00; skew -0.53</t>
         </is>
       </c>
     </row>
@@ -735,11 +735,11 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>mean 5.87, SD 1.12</t>
+          <t>mean 5.84, SD 1.12</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>alpha 0.871, rhoA 0.908, CR 0.909, AVE 0.715; min 1.00 max 7.00; skew -1.82</t>
+          <t>alpha 0.871, rhoA 0.908, CR 0.909, AVE 0.715; min 1.00 max 7.00; skew -1.70</t>
         </is>
       </c>
     </row>
@@ -770,11 +770,11 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>55.6% With Disclosure</t>
+          <t>56.2% With Disclosure</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -801,11 +801,11 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>47.0% High AIP</t>
+          <t>48.3% High AIP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,88 +1687,88 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E. PLS-SEM (seminr, 10,000 percentile bootstrap)</t>
+          <t>F. Indirect effects (percentile bootstrap)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>spec INT*PDPL-&gt;TRU (H7a tested via OLS Hayes PROCESS Model 1, Section G, not here)</t>
+          <t>REL-&gt;TRU-&gt;ENG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>beta=-0.110</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>t=-1.69</t>
-        </is>
-      </c>
+          <t>0.076</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[-0.235, 0.020]</t>
+          <t>[0.024, 0.142]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.098</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>f2=0.015</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Indirect-only mediation (full)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>direct beta 0.086 (p=0.218)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>E. PLS-SEM (seminr, 10,000 percentile bootstrap)</t>
+          <t>F. Indirect effects (percentile bootstrap)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>spec INT*DISC-&gt;TRU (H7b tested via OLS Hayes PROCESS Model 1, Section G, not here)</t>
+          <t>INT-&gt;TRU-&gt;ENG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>beta=0.004</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>t=0.06</t>
-        </is>
-      </c>
+          <t>-0.092</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[-0.130, 0.132]</t>
+          <t>[-0.155, -0.039]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.998</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>f2=0.000</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>&lt;.001</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Indirect-only mediation (full)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>direct beta -0.048 (p=0.415)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1778,38 +1778,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>REL-&gt;TRU-&gt;ENG</t>
+          <t>REL-&gt;ENG-&gt;PI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.050</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[0.024, 0.142]</t>
+          <t>[-0.027, 0.132]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Indirect-only mediation (full)</t>
+          <t>N/A (no direct path in model)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>direct beta 0.086 (p=0.218)</t>
+          <t>direct beta nan (p=nan)</t>
         </is>
       </c>
     </row>
@@ -1821,38 +1821,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INT-&gt;TRU-&gt;ENG</t>
+          <t>INT-&gt;ENG-&gt;PI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-0.092</t>
+          <t>-0.028</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[-0.155, -0.039]</t>
+          <t>[-0.093, 0.041]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;.001</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Indirect-only mediation (full)</t>
+          <t>Direct-only (no mediation)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>direct beta -0.048 (p=0.415)</t>
+          <t>direct beta -0.147 (p=0.001)</t>
         </is>
       </c>
     </row>
@@ -1864,27 +1864,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>REL-&gt;ENG-&gt;PI</t>
+          <t>REL-&gt;TRU-&gt;ENG-&gt;PI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.050</t>
+          <t>0.044</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[-0.027, 0.132]</t>
+          <t>[0.013, 0.087]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -1907,33 +1907,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>INT-&gt;ENG-&gt;PI</t>
+          <t>INT-&gt;TRU-&gt;ENG-&gt;PI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-0.028</t>
+          <t>-0.053</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[-0.093, 0.041]</t>
+          <t>[-0.095, -0.022]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>&lt;.001</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Direct-only (no mediation)</t>
+          <t>Complementary (partial)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -1945,55 +1945,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>F. Indirect effects (percentile bootstrap)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REL-&gt;TRU-&gt;ENG-&gt;PI</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>H7a beta_M (INT_x_PDPL) | all N (conclusions rest on this)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dampening, beta_M &lt; 0 (Amendment A-14)</t>
+        </is>
+      </c>
       <c r="D37" t="n">
         <v>381</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>b=-0.090</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[0.013, 0.087]</t>
+          <t>[-0.201, -0.007] BCa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>boot 0.048 (no Holm adjustment)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>f2=0.0162</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N/A (no direct path in model)</t>
+          <t>CI excludes 0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>direct beta nan (p=nan)</t>
+          <t>classical p=0.014; HC3 p=0.066; R2=0.115</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>F. Indirect effects (percentile bootstrap)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INT-&gt;TRU-&gt;ENG-&gt;PI</t>
+          <t>slope INT-&gt;TRU PDPL -1SD | all N (conclusions rest on this)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2002,92 +2010,76 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-0.053</t>
+          <t>slope=-0.124</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[-0.095, -0.022]</t>
+          <t>[-0.264, 0.044] BCa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>&lt;.001</t>
+          <t>boot 0.119</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Complementary (partial)</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>direct beta -0.147 (p=0.001)</t>
+          <t>conditional (base) effect, not moderation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H7a beta_M (INT_x_PDPL) | all N (conclusions rest on this)</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
-        </is>
-      </c>
+          <t>slope INT-&gt;TRU PDPL Mean | all N (conclusions rest on this)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
         <v>381</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>b=-0.092</t>
+          <t>slope=-0.225</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[-0.207, -0.005] BCa</t>
+          <t>[-0.334, -0.113] BCa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>boot 0.047 (no Holm adjustment)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>f2=0.0179</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>CI excludes 0</t>
-        </is>
-      </c>
+          <t>boot 0.000</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>classical p=0.010; HC3 p=0.077; R2=0.165</t>
+          <t>conditional (base) effect, not moderation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU PDPL -1SD | all N (conclusions rest on this)</t>
+          <t>slope INT-&gt;TRU PDPL +1SD | all N (conclusions rest on this)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2096,18 +2088,18 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>slope=-0.110</t>
+          <t>slope=-0.325</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[-0.251, 0.065] BCa</t>
+          <t>[-0.472, -0.173] BCa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>boot 0.180</t>
+          <t>boot 0.000</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2121,71 +2113,83 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU PDPL Mean | all N (conclusions rest on this)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>H7a beta_M (INT_x_PDPL) | without Cook's-D-flagged cases (sensitivity)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dampening, beta_M &lt; 0 (Amendment A-14)</t>
+        </is>
+      </c>
       <c r="D41" t="n">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>slope=-0.213</t>
+          <t>b=-0.106</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[-0.322, -0.097] BCa</t>
+          <t>[-0.172, -0.037] BCa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>boot 0.000</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>boot 0.006 (no Holm adjustment)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>f2=0.0163</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>CI excludes 0</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>conditional (base) effect, not moderation</t>
+          <t>classical p=0.018; HC3 p=0.001; R2=0.176</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU PDPL +1SD | all N (conclusions rest on this)</t>
+          <t>slope INT-&gt;TRU PDPL -1SD | without Cook's-D-flagged cases (sensitivity)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>slope=-0.315</t>
+          <t>slope=-0.149</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[-0.472, -0.158] BCa</t>
+          <t>[-0.261, -0.041] BCa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>boot 0.000</t>
+          <t>boot 0.008</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -2199,83 +2203,71 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H7a beta_M (INT_x_PDPL) | without Cook's-D-flagged cases (sensitivity)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
-        </is>
-      </c>
+          <t>slope INT-&gt;TRU PDPL Mean | without Cook's-D-flagged cases (sensitivity)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>b=-0.072</t>
+          <t>slope=-0.268</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[-0.126, -0.018] BCa</t>
+          <t>[-0.347, -0.184] BCa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>boot 0.018 (no Holm adjustment)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>f2=0.0120</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>CI excludes 0</t>
-        </is>
-      </c>
+          <t>boot 0.000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>classical p=0.044; HC3 p=0.004; R2=0.278</t>
+          <t>conditional (base) effect, not moderation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU PDPL -1SD | without Cook's-D-flagged cases (sensitivity)</t>
+          <t>slope INT-&gt;TRU PDPL +1SD | without Cook's-D-flagged cases (sensitivity)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>slope=-0.119</t>
+          <t>slope=-0.386</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[-0.209, -0.030] BCa</t>
+          <t>[-0.492, -0.274] BCa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>boot 0.012</t>
+          <t>boot 0.000</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2289,71 +2281,83 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU PDPL Mean | without Cook's-D-flagged cases (sensitivity)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>H7b beta_M (INT_x_DISC) | all N (conclusions rest on this)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dampening, beta_M &lt; 0 (Amendment A-14)</t>
+        </is>
+      </c>
       <c r="D45" t="n">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>slope=-0.200</t>
+          <t>b=-0.042</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[-0.279, -0.127] BCa</t>
+          <t>[-0.277, 0.192] BCa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>boot 0.000</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>boot 0.730 (no Holm adjustment)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>f2=0.0006</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>CI includes 0 -&gt; not supported</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>conditional (base) effect, not moderation</t>
+          <t>classical p=0.624; HC3 p=0.729; R2=0.093</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU PDPL +1SD | without Cook's-D-flagged cases (sensitivity)</t>
+          <t>slope INT-&gt;TRU DISC=0 | all N (conclusions rest on this)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>slope=-0.280</t>
+          <t>slope=-0.216</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[-0.389, -0.183] BCa</t>
+          <t>[-0.402, -0.026] BCa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>boot 0.000</t>
+          <t>boot 0.022</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2367,122 +2371,122 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H7b beta_M (INT_x_DISC) | all N (conclusions rest on this)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
-        </is>
-      </c>
+          <t>slope INT-&gt;TRU DISC=1 | all N (conclusions rest on this)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
         <v>381</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>b=-0.002</t>
+          <t>slope=-0.258</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[-0.233, 0.230] BCa</t>
+          <t>[-0.386, -0.117] BCa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>boot 0.978 (no Holm adjustment)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>f2=0.0000</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>CI includes 0 -&gt; not supported</t>
-        </is>
-      </c>
+          <t>boot 0.000</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>classical p=0.978; HC3 p=0.984; R2=0.150</t>
+          <t>conditional (base) effect, not moderation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU DISC=0 | all N (conclusions rest on this)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>H7b beta_M (INT_x_DISC) | without Cook's-D-flagged cases (sensitivity)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Dampening, beta_M &lt; 0 (Amendment A-14)</t>
+        </is>
+      </c>
       <c r="D48" t="n">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>slope=-0.218</t>
+          <t>b=-0.059</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[-0.407, -0.033] BCa</t>
+          <t>[-0.228, 0.106] BCa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>boot 0.024</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>boot 0.495 (no Holm adjustment)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>f2=0.0015</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CI includes 0 -&gt; not supported</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>conditional (base) effect, not moderation</t>
+          <t>classical p=0.477; HC3 p=0.484; R2=0.156</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>slope INT-&gt;TRU DISC=1 | all N (conclusions rest on this)</t>
+          <t>slope INT-&gt;TRU DISC=0 | without Cook's-D-flagged cases (sensitivity)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>slope=-0.220</t>
+          <t>slope=-0.264</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[-0.355, -0.078] BCa</t>
+          <t>[-0.399, -0.128] BCa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>boot 0.002</t>
+          <t>boot 0.000</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2496,127 +2500,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
+          <t>G. OLS Hayes PROCESS Model 1 (ESTIMATION OF RECORD for H7a/H7b, TF v2.14 A-15/A-16; INTERIM, BCa 5,000, no Holm)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H7b beta_M (INT_x_DISC) | without Cook's-D-flagged cases (sensitivity)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Dampening, beta_M &lt; 0 (this OLS check's own prediction, independent of Table 9's Buffering)</t>
-        </is>
-      </c>
+          <t>slope INT-&gt;TRU DISC=1 | without Cook's-D-flagged cases (sensitivity)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
         <v>349</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>b=-0.038</t>
+          <t>slope=-0.323</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[-0.182, 0.111] BCa</t>
+          <t>[-0.412, -0.228] BCa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>boot 0.612 (no Holm adjustment)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>f2=0.0008</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>CI includes 0 -&gt; not supported</t>
-        </is>
-      </c>
+          <t>boot 0.000</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
-        <is>
-          <t>classical p=0.607; HC3 p=0.616; R2=0.275</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>slope INT-&gt;TRU DISC=0 | without Cook's-D-flagged cases (sensitivity)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="n">
-        <v>349</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>slope=-0.169</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>[-0.286, -0.049] BCa</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>boot 0.004</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>conditional (base) effect, not moderation</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>G. OLS Hayes PROCESS Model 1 (SUPPLEMENTARY, not estimation of record; INTERIM, BCa 5,000, no Holm)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>slope INT-&gt;TRU DISC=1 | without Cook's-D-flagged cases (sensitivity)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="n">
-        <v>349</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>slope=-0.207</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>[-0.298, -0.119] BCa</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>boot 0.000</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
         <is>
           <t>conditional (base) effect, not moderation</t>
         </is>
